--- a/ZonasEscolares/excels/CUSCO-CUSCO-SAN_SEBASTIAN.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-SAN_SEBASTIAN.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_SEBASTIAN</t>
+          <t>SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CUSCO-CUSCO-SAN_SEBASTIAN.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-SAN_SEBASTIAN.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>PUKLLASUNCHIS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-13.53033</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-71.91124000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>739</v>
-      </c>
-      <c r="J2" t="n">
-        <v>46</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-13.53033</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-71.91124</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>SANTA MARIA GORETTI</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-13.5238</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-71.90634</v>
-      </c>
-      <c r="I3" t="n">
-        <v>259</v>
-      </c>
-      <c r="J3" t="n">
-        <v>28</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-13.5238</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-71.90634</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>SANTA MARIA MADRE DE DIOS</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-13.5331</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-71.91933</v>
-      </c>
-      <c r="I4" t="n">
-        <v>696</v>
-      </c>
-      <c r="J4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-13.5331</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-71.91933</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>334</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-13.53368</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-71.90912</v>
-      </c>
-      <c r="I5" t="n">
-        <v>266</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-13.53368</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-71.90912</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-13.5317</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-71.93847</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1232</v>
-      </c>
-      <c r="J6" t="n">
-        <v>59</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-13.5317</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-71.93847</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>427 KARI GRANDE</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-13.52353</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-71.94347999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>431</v>
-      </c>
-      <c r="J7" t="n">
-        <v>19</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-13.52353</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-71.94348</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>50868 FERNANDO TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-13.53994</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-71.9087</v>
-      </c>
-      <c r="I8" t="n">
-        <v>950</v>
-      </c>
-      <c r="J8" t="n">
-        <v>41</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-13.53994</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-71.9087</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>DIEGO QUISPE TITO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-13.52891</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-71.94019</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1754</v>
-      </c>
-      <c r="J9" t="n">
-        <v>85</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-13.52891</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-71.94019</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1754</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-13.53737</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-71.91027</v>
-      </c>
-      <c r="I10" t="n">
-        <v>521</v>
-      </c>
-      <c r="J10" t="n">
-        <v>41</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-13.53737</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-71.91027</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>LAURA VICUÑA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-13.53029</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-71.93861</v>
-      </c>
-      <c r="I11" t="n">
-        <v>20</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-13.53029</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-71.93861</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>CHASKA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-13.53032</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-71.93838</v>
-      </c>
-      <c r="I12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-13.53032</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-71.93838</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>GUADALUPE</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-13.52646</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-71.94129</v>
-      </c>
-      <c r="I13" t="n">
-        <v>268</v>
-      </c>
-      <c r="J13" t="n">
-        <v>17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-13.52646</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-71.94129</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>ARCO IRIS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-13.53321</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-71.92269</v>
-      </c>
-      <c r="I14" t="n">
-        <v>318</v>
-      </c>
-      <c r="J14" t="n">
-        <v>28</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-13.53321</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-71.92269</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>BOLIVARIANO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-13.540079</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-71.932011</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1112</v>
-      </c>
-      <c r="J15" t="n">
-        <v>50</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-13.540079</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-71.932011</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>INGENIERIA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-13.53093</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-71.93901</v>
-      </c>
-      <c r="I16" t="n">
-        <v>35</v>
-      </c>
-      <c r="J16" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-13.53093</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-71.93901</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>LA CASITA DE CARTON</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-13.52986</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-71.93143000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>20</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-13.52986</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-71.93143</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>PEDRO PAULET</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-13.53015</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-71.93656</v>
-      </c>
-      <c r="I18" t="n">
-        <v>108</v>
-      </c>
-      <c r="J18" t="n">
-        <v>10</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-13.53015</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-71.93656</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>MONTEVERDE</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-13.52515</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-71.90608</v>
-      </c>
-      <c r="I19" t="n">
-        <v>233</v>
-      </c>
-      <c r="J19" t="n">
-        <v>14</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-13.52515</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-71.90608</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>PERUANO SUIZO DE LOS ANDES</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-13.53375</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-71.93429</v>
-      </c>
-      <c r="I20" t="n">
-        <v>307</v>
-      </c>
-      <c r="J20" t="n">
-        <v>22</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-13.53375</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-71.93429</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>JESUS ES MI MAESTRO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-13.53408</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-71.91031</v>
-      </c>
-      <c r="I21" t="n">
-        <v>377</v>
-      </c>
-      <c r="J21" t="n">
-        <v>24</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-13.53408</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-71.91031</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>PEDRO PAULET MOSTAJO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-13.52739</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-71.94074999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>326</v>
-      </c>
-      <c r="J22" t="n">
-        <v>26</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-13.52739</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-71.94075</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>SAN JOSE LA SALLE</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-13.554118</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-71.943905</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1305</v>
-      </c>
-      <c r="J23" t="n">
-        <v>77</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-13.554118</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-71.943905</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/CUSCO-CUSCO-SAN_SEBASTIAN.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-SAN_SEBASTIAN.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>147083</t>
+          <t>148153</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PUKLLASUNCHIS</t>
+          <t>LAURA VICUÑA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.53033</t>
+          <t>-13.53029</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.91124</t>
+          <t>-71.93861</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>147375</t>
+          <t>599961</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SANTA MARIA GORETTI</t>
+          <t>PEDRO PAULET</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.5238</t>
+          <t>-13.53015</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.90634</t>
+          <t>-71.93656</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>108</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>147889</t>
+          <t>147969</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SANTA MARIA MADRE DE DIOS</t>
+          <t>334</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.5331</t>
+          <t>-13.53368</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.91933</t>
+          <t>-71.90912</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>147969</t>
+          <t>602671</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>MONTEVERDE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.53368</t>
+          <t>-13.52515</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.90912</t>
+          <t>-71.90608</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>148006</t>
+          <t>148228</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VIRGEN DE FATIMA</t>
+          <t>GUADALUPE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.5317</t>
+          <t>-13.52646</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.93847</t>
+          <t>-71.94129</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>148073</t>
+          <t>599193</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50868 FERNANDO TUPAC AMARU</t>
+          <t>LA CASITA DE CARTON</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.53994</t>
+          <t>-13.52986</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.9087</t>
+          <t>-71.93143</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>148105</t>
+          <t>693464</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DIEGO QUISPE TITO</t>
+          <t>PERUANO SUIZO DE LOS ANDES</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.52891</t>
+          <t>-13.53375</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.94019</t>
+          <t>-71.93429</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>148134</t>
+          <t>748640</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>JESUS ES MI MAESTRO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.53737</t>
+          <t>-13.53408</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.91027</t>
+          <t>-71.91031</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>377</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>148153</t>
+          <t>803207</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LAURA VICUÑA</t>
+          <t>PEDRO PAULET MOSTAJO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.53029</t>
+          <t>-13.52739</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.93861</t>
+          <t>-71.94075</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>326</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>148209</t>
+          <t>147375</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CHASKA</t>
+          <t>SANTA MARIA GORETTI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.53032</t>
+          <t>-13.5238</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.93838</t>
+          <t>-71.90634</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>148266</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>GUADALUPE</t>
+          <t>ARCO IRIS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.52646</t>
+          <t>-13.53321</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.94129</t>
+          <t>-71.92269</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>148266</t>
+          <t>148209</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ARCO IRIS</t>
+          <t>CHASKA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.53321</t>
+          <t>-13.53032</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.92269</t>
+          <t>-71.93838</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>520915</t>
+          <t>147889</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BOLIVARIANO</t>
+          <t>SANTA MARIA MADRE DE DIOS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.540079</t>
+          <t>-13.5331</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.932011</t>
+          <t>-71.91933</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>696</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>570892</t>
+          <t>148073</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>INGENIERIA</t>
+          <t>50868 FERNANDO TUPAC AMARU</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.53093</t>
+          <t>-13.53994</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.93901</t>
+          <t>-71.9087</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>950</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>599193</t>
+          <t>148134</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LA CASITA DE CARTON</t>
+          <t>VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.52986</t>
+          <t>-13.53737</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.93143</t>
+          <t>-71.91027</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>521</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>599961</t>
+          <t>147083</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PEDRO PAULET</t>
+          <t>PUKLLASUNCHIS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.53015</t>
+          <t>-13.53033</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.93656</t>
+          <t>-71.91124</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>739</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>602671</t>
+          <t>520915</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MONTEVERDE</t>
+          <t>BOLIVARIANO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.52515</t>
+          <t>-13.540079</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.90608</t>
+          <t>-71.932011</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>693464</t>
+          <t>148006</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PERUANO SUIZO DE LOS ANDES</t>
+          <t>VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-13.53375</t>
+          <t>-13.5317</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.93429</t>
+          <t>-71.93847</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>748640</t>
+          <t>570892</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JESUS ES MI MAESTRO</t>
+          <t>INGENIERIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.53408</t>
+          <t>-13.53093</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.91031</t>
+          <t>-71.93901</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>803207</t>
+          <t>863692</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PEDRO PAULET MOSTAJO</t>
+          <t>SAN JOSE LA SALLE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.52739</t>
+          <t>-13.554118</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.94075</t>
+          <t>-71.943905</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>863692</t>
+          <t>148105</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN JOSE LA SALLE</t>
+          <t>DIEGO QUISPE TITO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.554118</t>
+          <t>-13.52891</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.943905</t>
+          <t>-71.94019</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">

--- a/ZonasEscolares/excels/CUSCO-CUSCO-SAN_SEBASTIAN.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-SAN_SEBASTIAN.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>148153</t>
+          <t>863692</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LAURA VICUÑA</t>
+          <t>SAN JOSE LA SALLE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.53029</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.93861</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-13.554118</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-71.943905</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>599961</t>
+          <t>803207</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PEDRO PAULET</t>
+          <t>PEDRO PAULET MOSTAJO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.53015</t>
+          <t>326</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.93656</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>-13.52739</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-71.94075</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>147969</t>
+          <t>748640</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>JESUS ES MI MAESTRO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.53368</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.90912</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-13.53408</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-71.91031</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>602671</t>
+          <t>693464</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MONTEVERDE</t>
+          <t>PERUANO SUIZO DE LOS ANDES</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.52515</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.90608</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-13.53375</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-71.93429</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>148228</t>
+          <t>602671</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GUADALUPE</t>
+          <t>MONTEVERDE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.52646</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.94129</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-13.52515</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.90608</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>148054</t>
+          <t>599961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>427 KARI GRANDE</t>
+          <t>PEDRO PAULET</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.52353</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.94348</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>-13.53015</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-71.93656</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -883,22 +883,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>-13.52986</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>-71.93143</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>693464</t>
+          <t>570892</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PERUANO SUIZO DE LOS ANDES</t>
+          <t>INGENIERIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.53375</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.93429</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-13.53093</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-71.93901</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>748640</t>
+          <t>520915</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JESUS ES MI MAESTRO</t>
+          <t>BOLIVARIANO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.53408</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.91031</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>-13.540079</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-71.932011</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>803207</t>
+          <t>148266</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PEDRO PAULET MOSTAJO</t>
+          <t>ARCO IRIS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.52739</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.94075</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>-13.53321</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.92269</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>147375</t>
+          <t>148228</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SANTA MARIA GORETTI</t>
+          <t>GUADALUPE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.5238</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.90634</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-13.52646</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-71.94129</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>148266</t>
+          <t>148209</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ARCO IRIS</t>
+          <t>CHASKA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.53321</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.92269</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-13.53032</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-71.93838</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>148209</t>
+          <t>148153</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CHASKA</t>
+          <t>LAURA VICUÑA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.53032</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.93838</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-13.53029</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-71.93861</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>147889</t>
+          <t>148134</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SANTA MARIA MADRE DE DIOS</t>
+          <t>VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.5331</t>
+          <t>521</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.91933</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>-13.53737</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-71.91027</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>148073</t>
+          <t>148105</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>50868 FERNANDO TUPAC AMARU</t>
+          <t>DIEGO QUISPE TITO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.53994</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.9087</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>-13.52891</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-71.94019</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>148134</t>
+          <t>148073</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>50868 FERNANDO TUPAC AMARU</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.53737</t>
+          <t>950</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.91027</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>-13.53994</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-71.9087</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>147083</t>
+          <t>148054</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PUKLLASUNCHIS</t>
+          <t>427 KARI GRANDE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.53033</t>
+          <t>431</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.91124</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>-13.52353</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-71.94348</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>520915</t>
+          <t>148006</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BOLIVARIANO</t>
+          <t>VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.540079</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.932011</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>-13.5317</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-71.93847</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>148006</t>
+          <t>147969</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VIRGEN DE FATIMA</t>
+          <t>334</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-13.5317</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.93847</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>-13.53368</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-71.90912</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>570892</t>
+          <t>147889</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>INGENIERIA</t>
+          <t>SANTA MARIA MADRE DE DIOS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.53093</t>
+          <t>696</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.93901</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-13.5331</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-71.91933</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>863692</t>
+          <t>147375</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN JOSE LA SALLE</t>
+          <t>SANTA MARIA GORETTI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.554118</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.943905</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>-13.5238</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>-71.90634</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>148105</t>
+          <t>147083</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>DIEGO QUISPE TITO</t>
+          <t>PUKLLASUNCHIS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.52891</t>
+          <t>739</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.94019</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>-13.53033</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-71.91124</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">

--- a/ZonasEscolares/excels/CUSCO-CUSCO-SAN_SEBASTIAN.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-SAN_SEBASTIAN.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
